--- a/stories/arbres/ATOM-SEC.RUE.003-05.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>César sort avec maman. Ils marchent dans la rue. César reste près de l'adulte. Il prend la main de maman. Il tient aussi le manteau. Main ou manteau. Ses pieds marchent à côté. Maman dit : près de moi. César sent le manteau. Le manteau est doux. La main de maman est chaude. César marche à côté. Ils passent la boulangerie. César sent le pain chaud. Il reste près de l'adulte. La main tient le manteau. Maman sourit. César sourit aussi. Ils rentrent ensemble. César garde la main. Il reste près de l'adulte.</t>
+          <t>César sort avec maman. Ils marchent dans la rue. César reste près de l'adulte. Il prend la main de maman. Il tient aussi le manteau. Main ou manteau. Ses pieds marchent à côté. Près de moi. César sent le manteau. Le manteau est doux. La main de maman est chaude. César marche à côté. Ils passent la boulangerie. César sent le pain chaud. Il reste près de l'adulte. La main tient le manteau. Maman sourit. César sourit aussi. Ils rentrent ensemble. César garde la main. Il reste près de l'adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|César sort avec maman. Ils marchent dans la rue. César reste près de l'adulte. Il prend la main de maman. Il tient aussi le manteau. Main ou manteau. Ses pieds marchent à côté.
+maman|Près de moi.
+narrateur|César sent le manteau. Le manteau est doux. La main de maman est chaude. César marche à côté. Ils passent la boulangerie. César sent le pain chaud. Il reste près de l'adulte. La main tient le manteau. Maman sourit. César sourit aussi. Ils rentrent ensemble. César garde la main. Il reste près de l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|César marche dans la rue. Où est-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|César est près de maman. La main tient le manteau. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1840,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|César garde la main de maman. Ils rentrent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2007,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2047,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.003-05.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|César sent le manteau. Le manteau est doux. La main de maman est chaude. César marche à côté. Ils passent la boulangerie. César sent le pain chaud. Il reste près de l'adulte. La main tient le manteau. Maman sourit. César sourit aussi. Ils rentrent ensemble. César garde la main. Il reste près de l'adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|César marche dans la rue. Où est-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|César est près de maman. La main tient le manteau. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1845,6 +1853,7 @@
           <t>narrateur|César garde la main de maman. Ils rentrent à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2012,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.003-05.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>César près de maman</t>
+          <t>La feuille de la fontaine</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut poser une feuille jaune dans la fontaine. Une éclaboussure mouille sa chaussure. Elle reste près de maman. Puis la feuille tourne dans l'eau.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>César sort avec maman. Ils marchent dans la rue. César reste près de l'adulte. Il prend la main de maman. Il tient aussi le manteau. Main ou manteau. Ses pieds marchent à côté. Près de moi. César sent le manteau. Le manteau est doux. La main de maman est chaude. César marche à côté. Ils passent la boulangerie. César sent le pain chaud. Il reste près de l'adulte. La main tient le manteau. Maman sourit. César sourit aussi. Ils rentrent ensemble. César garde la main. Il reste près de l'adulte.</t>
+          <t>L'eau de la fontaine chante sur la pierre. Une feuille jaune tremble au bord. Ça sent la mousse et le froid. La place du village est calme. Un pigeon boit, tout petit. Mila vit ici, avec maman. Maman, l'eau chante ! Oui. Elle est toute claire. Tu as vu la feuille jaune ? Elle veut nager. En ce moment, Mila prend la main. La main de maman est tiède. Je veux la mettre dans l'eau ! On y va. Tu restes près de moi. Elles marchent sur les dalles. Les dalles sont un peu humides. L'eau saute et retombe. Elle fait des ronds ! Oui. Une goutte plus grosse éclabousse. La chaussure de Mila devient sombre. Oh, c'est mouillé ! L'eau a sauté. Tu restes près de moi ? Oui. Mila se serre contre maman. Elle garde la main. Bravo. La feuille jaune attend encore. L'eau chante, plus douce. On s'approche tout doux ? Tout doux. Leurs pieds restent près. La pierre de la vasque est froide. Tu tiens ma main ? Oui, maman. Mila tend la feuille, tout près. Maman l'aide, juste à côté. Elle flotte ! Merci d'être restée près. La feuille tourne dans un petit rond. L'eau claire la porte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;César sort avec maman. Ils marchent dans la rue. César reste &lt;emphasis level="moderate"&gt;près&lt;/emphasis&gt; de l'adulte. Il prend la main de maman. Il tient aussi le manteau. Main ou manteau. Ses pieds marchent à côté. Maman dit : près de moi. César sent le manteau. Le manteau est doux. La main de maman est chaude. César marche à côté. Ils passent la boulangerie. César sent le pain chaud. Il reste près de l'adulte. La main tient le manteau. Maman sourit. César sourit aussi. Ils rentrent ensemble. César garde la main. Il reste près de l'adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'eau de la fontaine chante sur la pierre. Une feuille jaune tremble au bord. Ça sent la mousse et le froid. La place du village est calme. Un pigeon boit, tout petit. Mila vit ici, avec maman. Maman, l'eau chante ! Oui. Elle est toute claire. Tu as vu la feuille jaune ? Elle veut nager. En ce moment, Mila prend la main. La main de maman est tiède. Je veux la mettre dans l'eau ! On y va. Tu restes près de moi. Elles marchent sur les dalles. Les dalles sont un peu humides. L'eau saute et retombe. Elle fait des ronds ! Oui. Une goutte plus grosse éclabousse. La chaussure de Mila devient sombre. Oh, c'est mouillé ! L'eau a sauté. Tu restes près de moi ? Oui. Mila se serre contre maman. Elle garde la main. Bravo. La feuille jaune attend encore. L'eau chante, plus douce. On s'approche tout doux ? Tout doux. Leurs pieds restent près. La pierre de la vasque est froide. Tu tiens ma main ? Oui, maman. Mila tend la feuille, tout près. Maman l'aide, juste à côté. Elle flotte ! Merci d'être restée près. La feuille tourne dans un petit rond. L'eau claire la porte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,12 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|César sort avec maman. Ils marchent dans la rue. César reste près de l'adulte. Il prend la main de maman. Il tient aussi le manteau. Main ou manteau. Ses pieds marchent à côté.
-maman|Près de moi.
-narrateur|César sent le manteau. Le manteau est doux. La main de maman est chaude. César marche à côté. Ils passent la boulangerie. César sent le pain chaud. Il reste près de l'adulte. La main tient le manteau. Maman sourit. César sourit aussi. Ils rentrent ensemble. César garde la main. Il reste près de l'adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|L'eau de la fontaine chante sur la pierre.
+narrateur|Une feuille jaune tremble au bord.
+narrateur|Ça sent la mousse et le froid.
+narrateur|La place du village est calme.
+narrateur|Un pigeon boit, tout petit.
+narrateur|Mila vit ici, avec maman.
+enfant-f|Maman, l'eau chante !
+maman|Oui.
+maman|Elle est toute claire.
+maman|Tu as vu la feuille jaune ?
+enfant-f|Elle veut nager.
+narrateur|En ce moment, Mila prend la main.
+narrateur|La main de maman est tiède.
+enfant-f|Je veux la mettre dans l'eau !
+maman|On y va.
+maman|Tu restes près de moi.
+narrateur|Elles marchent sur les dalles.
+narrateur|Les dalles sont un peu humides.
+narrateur|L'eau saute et retombe.
+enfant-f|Elle fait des ronds !
+maman|Oui.
+narrateur|Une goutte plus grosse éclabousse.
+narrateur|La chaussure de Mila devient sombre.
+enfant-f|Oh, c'est mouillé !
+maman|L'eau a sauté.
+maman|Tu restes près de moi ?
+enfant-f|Oui.
+narrateur|Mila se serre contre maman.
+narrateur|Elle garde la main.
+maman|Bravo.
+narrateur|La feuille jaune attend encore.
+narrateur|L'eau chante, plus douce.
+maman|On s'approche tout doux ?
+enfant-f|Tout doux.
+narrateur|Leurs pieds restent près.
+narrateur|La pierre de la vasque est froide.
+maman|Tu tiens ma main ?
+enfant-f|Oui, maman.
+narrateur|Mila tend la feuille, tout près.
+narrateur|Maman l'aide, juste à côté.
+enfant-f|Elle flotte !
+maman|Merci d'être restée près.
+narrateur|La feuille tourne dans un petit rond.
+narrateur|L'eau claire la porte.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,12 +1399,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>César marche dans la rue. Où est-il ?</t>
+          <t>Mila marche près de la fontaine. Où est-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;César marche dans la rue. Où est-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila marche près de la fontaine. Où est-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1362,7 +1419,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>près de maman | près | la main | manteau | à côté</t>
+          <t>près | près de maman | à côté | la main | contre maman</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1377,7 +1434,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il reste près. Il tient la main. Où est César ?</t>
+          <t>Elle reste près de maman. Où est Mila ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1426,7 +1483,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,10 +1559,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|César marche dans la rue. Où est-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Mila marche près de la fontaine.
+narrateur|Où est-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>César est près de maman. La main tient le manteau. Maman est là.</t>
+          <t>Mila est près de maman. La main tient la main. Elle s'est serrée contre maman. Tu es restée près de moi ? Oui. J'ai tenu ta main. Bravo, Mila. Près de moi. La main de maman reste tiède. La chaussure sèche un peu. La feuille jaune tourne encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;César est &lt;emphasis level="moderate"&gt;près&lt;/emphasis&gt; de maman. La main tient le manteau. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila est près de maman. La main tient la main. Elle s'est serrée contre maman. Tu es restée près de moi ? Oui. J'ai tenu ta main. Bravo, Mila. Près de moi. La main de maman reste tiède. La chaussure sèche un peu. La feuille jaune tourne encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1591,14 +1648,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1678,10 +1735,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|César est près de maman. La main tient le manteau. Maman est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila est près de maman.
+narrateur|La main tient la main.
+narrateur|Elle s'est serrée contre maman.
+maman|Tu es restée près de moi ?
+enfant-f|Oui.
+enfant-f|J'ai tenu ta main.
+maman|Bravo, Mila.
+maman|Près de moi.
+narrateur|La main de maman reste tiède.
+narrateur|La chaussure sèche un peu.
+narrateur|La feuille jaune tourne encore.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,12 +1772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>César garde la main de maman. Ils rentrent à la maison.</t>
+          <t>Elles regardent l'eau ensemble. Tu vois ta feuille ? Mila pose le menton sur la pierre. Elle fait un bateau ! Oui. Tu es restée près. L'eau est froide sous un doigt. La mousse est toute verte, toute douce. Ça sent la pierre mouillée. Oui. Mila garde la main de maman. La feuille passe sous un filet d'eau. Elle brille ! Oui. On rentre près l'une de l'autre. Les dalles sèchent au soleil. Le pigeon s'envole vers le toit. La fontaine chante encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;César garde la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman. Ils rentrent à la maison.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Elles regardent l'eau ensemble. Tu vois ta feuille ? Mila pose le menton sur la pierre. Elle fait un bateau ! Oui. Tu es restée près. L'eau est froide sous un doigt. La mousse est toute verte, toute douce. Ça sent la pierre mouillée. Oui. Mila garde la main de maman. La feuille passe sous un filet d'eau. Elle brille ! Oui. On rentre près l'une de l'autre. Les dalles sèchent au soleil. Le pigeon s'envole vers le toit. La fontaine chante encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1767,14 +1833,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1850,10 +1916,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|César garde la main de maman. Ils rentrent à la maison.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Elles regardent l'eau ensemble.
+maman|Tu vois ta feuille ?
+narrateur|Mila pose le menton sur la pierre.
+enfant-f|Elle fait un bateau !
+maman|Oui.
+maman|Tu es restée près.
+narrateur|L'eau est froide sous un doigt.
+narrateur|La mousse est toute verte, toute douce.
+enfant-f|Ça sent la pierre mouillée.
+maman|Oui.
+narrateur|Mila garde la main de maman.
+narrateur|La feuille passe sous un filet d'eau.
+enfant-f|Elle brille !
+maman|Oui.
+maman|On rentre près l'une de l'autre.
+narrateur|Les dalles sèchent au soleil.
+narrateur|Le pigeon s'envole vers le toit.
+narrateur|La fontaine chante encore.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1878,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Ma feuille nage. Oui. Merci d'être restée près. Un rond d'eau s'élargit. La feuille jaune tourne dans l'eau claire.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ma feuille nage. Oui. Merci d'être restée près. Un rond d'eau s'élargit. La feuille jaune tourne dans l'eau claire.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1939,14 +2021,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2018,10 +2100,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Ma feuille nage.
+maman|Oui.
+maman|Merci d'être restée près.
+narrateur|Un rond d'eau s'élargit.
+narrateur|La feuille jaune tourne dans l'eau claire.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2040,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.003-05.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rue vers la boulangerie</t>
+          <t>place du village, fontaine de pierre, fin de matin</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>César, maman</t>
+          <t>Mila, maman</t>
         </is>
       </c>
     </row>
